--- a/exports/INDHOTEL_full_report.xlsx
+++ b/exports/INDHOTEL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:U74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>10.03</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44585.38541666666</v>
+        <v>44585.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>198.55</v>
+        <v>193.8</v>
       </c>
       <c r="I2" t="n">
         <v>198.1483852788908</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4</v>
+        <v>-0.05</v>
       </c>
       <c r="L2" t="n">
         <v>5.11</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>9.08</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44589.55208333334</v>
+        <v>44592.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>207.05</v>
+        <v>215.35</v>
       </c>
       <c r="I3" t="n">
         <v>211.3642075401575</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.84</v>
+        <v>-11.12</v>
       </c>
       <c r="L3" t="n">
-        <v>9.26</v>
+        <v>12.72</v>
       </c>
       <c r="M3" t="n">
-        <v>0.52</v>
+        <v>0.7</v>
       </c>
       <c r="N3" t="n">
-        <v>2.53</v>
+        <v>4.25</v>
       </c>
       <c r="O3" t="n">
         <v>-6.33</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>9.84</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>206.55</v>
+        <v>199.85</v>
       </c>
       <c r="I4" t="n">
         <v>202.2484205583277</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.09</v>
+        <v>-7.2</v>
       </c>
       <c r="L4" t="n">
-        <v>4.67</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>1.19</v>
+        <v>2.71</v>
       </c>
       <c r="N4" t="n">
-        <v>4.37</v>
+        <v>6.08</v>
       </c>
       <c r="O4" t="n">
         <v>4.25</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.07</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44628.55208333334</v>
+        <v>44629.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>194.95</v>
+        <v>207.1</v>
       </c>
       <c r="I5" t="n">
         <v>203.6397558670681</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K5" t="n">
-        <v>2.45</v>
+        <v>-3.63</v>
       </c>
       <c r="L5" t="n">
         <v>5.7</v>
@@ -726,7 +785,7 @@
         <v>3.04</v>
       </c>
       <c r="N5" t="n">
-        <v>5.93</v>
+        <v>6.69</v>
       </c>
       <c r="O5" t="n">
         <v>-6.08</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>12.44</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>241.5</v>
+        <v>232</v>
       </c>
       <c r="I6" t="n">
         <v>235.4063934510251</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K6" t="n">
-        <v>16.61</v>
+        <v>12.02</v>
       </c>
       <c r="L6" t="n">
         <v>5.09</v>
       </c>
       <c r="M6" t="n">
-        <v>0.83</v>
+        <v>1.41</v>
       </c>
       <c r="N6" t="n">
         <v>3.2</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>11.67</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44679.55208333334</v>
+        <v>44680.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>247.5</v>
+        <v>257.15</v>
       </c>
       <c r="I7" t="n">
         <v>255.34989532512</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.68</v>
+        <v>-10.84</v>
       </c>
       <c r="L7" t="n">
-        <v>7.67</v>
+        <v>12.16</v>
       </c>
       <c r="M7" t="n">
         <v>0.91</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>10.84</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44690.38541666666</v>
+        <v>44690.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>240.25</v>
+        <v>238.55</v>
       </c>
       <c r="I8" t="n">
         <v>239.1451696758932</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>-6.57</v>
+        <v>-7.23</v>
       </c>
       <c r="L8" t="n">
-        <v>6.81</v>
+        <v>7.76</v>
       </c>
       <c r="M8" t="n">
         <v>3.03</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44735.55208333334</v>
+        <v>44736.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>223.75</v>
+        <v>226.85</v>
       </c>
       <c r="I9" t="n">
         <v>226.6529807087309</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>45</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="K9" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="L9" t="n">
         <v>1.03</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.06</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44846.55208333334</v>
+        <v>44847.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>329.7</v>
+        <v>314.15</v>
       </c>
       <c r="I10" t="n">
         <v>321.0589997381732</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>110.1666666666667</v>
+        <v>111</v>
       </c>
       <c r="K10" t="n">
-        <v>45.34</v>
+        <v>38.48</v>
       </c>
       <c r="L10" t="n">
         <v>2.84</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>150</v>
+        <v>151</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>10.39</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44865.38541666666</v>
+        <v>44865.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>332.1</v>
+        <v>333.5</v>
       </c>
       <c r="I11" t="n">
         <v>332.227421990485</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.71</v>
+        <v>-6.16</v>
       </c>
       <c r="L11" t="n">
-        <v>6.05</v>
+        <v>6.53</v>
       </c>
       <c r="M11" t="n">
         <v>2.14</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>5.22</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44875.55208333334</v>
+        <v>44876.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>339.5</v>
+        <v>314.65</v>
       </c>
       <c r="I12" t="n">
         <v>326.5452610020149</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>1.8</v>
+        <v>-5.65</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6899999999999999</v>
+        <v>6.34</v>
       </c>
       <c r="M12" t="n">
         <v>0.44</v>
       </c>
       <c r="N12" t="n">
-        <v>1.78</v>
+        <v>6.86</v>
       </c>
       <c r="O12" t="n">
         <v>3.33</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>13.91</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44909.55208333334</v>
+        <v>44910.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>333</v>
+        <v>334.65</v>
       </c>
       <c r="I13" t="n">
         <v>334.0542435962527</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.83</v>
+        <v>-6.36</v>
       </c>
       <c r="L13" t="n">
         <v>10.92</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>4.31</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44915.55208333334</v>
+        <v>44916.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>323.5</v>
+        <v>311.9</v>
       </c>
       <c r="I14" t="n">
         <v>320.2374239156473</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.33</v>
+        <v>-6.8</v>
       </c>
       <c r="L14" t="n">
-        <v>4.3</v>
+        <v>6.98</v>
       </c>
       <c r="M14" t="n">
         <v>0.34</v>
       </c>
       <c r="N14" t="n">
-        <v>1.58</v>
+        <v>4.22</v>
       </c>
       <c r="O14" t="n">
         <v>-0.23</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44956.55208333334</v>
+        <v>44958.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>292</v>
+        <v>327.45</v>
       </c>
       <c r="I15" t="n">
         <v>302.6597842178979</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K15" t="n">
-        <v>6.38</v>
+        <v>-4.99</v>
       </c>
       <c r="L15" t="n">
-        <v>4.86</v>
+        <v>5.27</v>
       </c>
       <c r="M15" t="n">
-        <v>0.83</v>
+        <v>8.9</v>
       </c>
       <c r="N15" t="n">
-        <v>4.91</v>
+        <v>11.3</v>
       </c>
       <c r="O15" t="n">
         <v>-4.22</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>10.92</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44978.55208333334</v>
+        <v>44979.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>309.4</v>
+        <v>301.6</v>
       </c>
       <c r="I16" t="n">
         <v>306.6587704576584</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.51</v>
+        <v>-7.89</v>
       </c>
       <c r="L16" t="n">
-        <v>5.73</v>
+        <v>8.18</v>
       </c>
       <c r="M16" t="n">
         <v>0.92</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>3.26</v>
       </c>
       <c r="O16" t="n">
         <v>11.3</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.57</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44985.55208333334</v>
+        <v>44986.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>310.2</v>
+        <v>316</v>
       </c>
       <c r="I17" t="n">
         <v>315.9214966835614</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.85</v>
+        <v>-4.77</v>
       </c>
       <c r="L17" t="n">
         <v>5.55</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.98</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44998.38541666666</v>
+        <v>44998.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>314.65</v>
+        <v>312</v>
       </c>
       <c r="I18" t="n">
         <v>313.8682994160395</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.43</v>
+        <v>-1.27</v>
       </c>
       <c r="L18" t="n">
         <v>2.06</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>4.9</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45014.38541666666</v>
+        <v>45014.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>314.1</v>
+        <v>319.75</v>
       </c>
       <c r="I19" t="n">
         <v>319.62234420229</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.67</v>
+        <v>-2.48</v>
       </c>
       <c r="L19" t="n">
         <v>3.97</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.68</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45061.38541666666</v>
+        <v>45061.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>356.3</v>
+        <v>353.25</v>
       </c>
       <c r="I20" t="n">
         <v>355.6844011094682</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>46.83333333333334</v>
+        <v>47</v>
       </c>
       <c r="K20" t="n">
-        <v>11.43</v>
+        <v>10.48</v>
       </c>
       <c r="L20" t="n">
         <v>1.77</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.88</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45065.55208333334</v>
+        <v>45068.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>372.7</v>
+        <v>374.75</v>
       </c>
       <c r="I21" t="n">
         <v>374.0087046213863</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.51</v>
+        <v>-6.09</v>
       </c>
       <c r="L21" t="n">
         <v>6.55</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.18</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45098.55208333334</v>
+        <v>45099.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>396.7</v>
+        <v>383.4</v>
       </c>
       <c r="I22" t="n">
         <v>385.103650577748</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K22" t="n">
-        <v>5.86</v>
+        <v>2.31</v>
       </c>
       <c r="L22" t="n">
         <v>1.69</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>6.34</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45126.38541666666</v>
+        <v>45126.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>392.15</v>
+        <v>401.9</v>
       </c>
       <c r="I23" t="n">
         <v>397.8781251157908</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.28</v>
+        <v>-4.83</v>
       </c>
       <c r="L23" t="n">
-        <v>3.94</v>
+        <v>5.11</v>
       </c>
       <c r="M23" t="n">
         <v>0.88</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>5.79</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45155.55208333334</v>
+        <v>45156.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>382</v>
+        <v>379.7</v>
       </c>
       <c r="I24" t="n">
         <v>381.3126551917628</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.95</v>
+        <v>-5.52</v>
       </c>
       <c r="L24" t="n">
-        <v>5.95</v>
+        <v>6.22</v>
       </c>
       <c r="M24" t="n">
         <v>1.51</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>4.18</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45160.55208333334</v>
+        <v>45161.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>388.5</v>
+        <v>400.25</v>
       </c>
       <c r="I25" t="n">
         <v>394.0535869000922</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.32</v>
+        <v>-5.41</v>
       </c>
       <c r="L25" t="n">
-        <v>2.55</v>
+        <v>7.57</v>
       </c>
       <c r="M25" t="n">
         <v>0.09</v>
       </c>
       <c r="N25" t="n">
-        <v>2.32</v>
+        <v>3.32</v>
       </c>
       <c r="O25" t="n">
         <v>-0.35</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.58</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45181.55208333334</v>
+        <v>45182.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>420</v>
+        <v>412.65</v>
       </c>
       <c r="I26" t="n">
         <v>413.1438266988833</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K26" t="n">
-        <v>4.93</v>
+        <v>3.1</v>
       </c>
       <c r="L26" t="n">
         <v>3.25</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>5.5</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45236.55208333334</v>
+        <v>45237.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>395.5</v>
+        <v>399.95</v>
       </c>
       <c r="I27" t="n">
         <v>397.8467667119069</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K27" t="n">
-        <v>4.16</v>
+        <v>3.08</v>
       </c>
       <c r="L27" t="n">
         <v>4.68</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.66</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>439.75</v>
+        <v>423.85</v>
       </c>
       <c r="I28" t="n">
         <v>428.5995918224486</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K28" t="n">
-        <v>9.949999999999999</v>
+        <v>5.98</v>
       </c>
       <c r="L28" t="n">
         <v>1.44</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>6.99</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45293.55208333334</v>
+        <v>45294.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>438.2</v>
+        <v>451.4</v>
       </c>
       <c r="I29" t="n">
         <v>445.8438792747623</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.39</v>
+        <v>-6.5</v>
       </c>
       <c r="L29" t="n">
-        <v>4.66</v>
+        <v>7.35</v>
       </c>
       <c r="M29" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>1.94</v>
+        <v>3.09</v>
       </c>
       <c r="O29" t="n">
         <v>-4.43</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.25</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>569.9</v>
+        <v>553.95</v>
       </c>
       <c r="I30" t="n">
         <v>560.5615268878546</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>69.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K30" t="n">
-        <v>26.25</v>
+        <v>22.72</v>
       </c>
       <c r="L30" t="n">
         <v>2.97</v>
@@ -2151,7 +2510,7 @@
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.04</v>
+        <v>4.35</v>
       </c>
       <c r="O30" t="n">
         <v>3.09</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>8.58</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45377.55208333334</v>
+        <v>45378.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>569.5</v>
+        <v>589.6</v>
       </c>
       <c r="I31" t="n">
         <v>584.4979210930281</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.81</v>
+        <v>-6.44</v>
       </c>
       <c r="L31" t="n">
-        <v>4.21</v>
+        <v>7.05</v>
       </c>
       <c r="M31" t="n">
         <v>0.71</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.75</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45398.38541666666</v>
+        <v>45398.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>589.55</v>
+        <v>584</v>
       </c>
       <c r="I32" t="n">
         <v>587.8144922170236</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.01</v>
+        <v>-0.95</v>
       </c>
       <c r="L32" t="n">
         <v>3.87</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.05</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45436.55208333334</v>
+        <v>45439.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>567.5</v>
+        <v>583.45</v>
       </c>
       <c r="I33" t="n">
         <v>574.375319808948</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>38</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K33" t="n">
-        <v>2.83</v>
+        <v>0.09</v>
       </c>
       <c r="L33" t="n">
         <v>5.39</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>5.76</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45442.55208333334</v>
+        <v>45443.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>556.55</v>
+        <v>549</v>
       </c>
       <c r="I34" t="n">
         <v>555.5793996568607</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.61</v>
+        <v>-5.9</v>
       </c>
       <c r="L34" t="n">
-        <v>4.93</v>
+        <v>6.2</v>
       </c>
       <c r="M34" t="n">
         <v>0.07000000000000001</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>6.09</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45449.38541666666</v>
+        <v>45449.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>583</v>
+        <v>584.65</v>
       </c>
       <c r="I35" t="n">
         <v>583.4046834777289</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.19</v>
+        <v>-6.49</v>
       </c>
       <c r="L35" t="n">
-        <v>6.47</v>
+        <v>6.52</v>
       </c>
       <c r="M35" t="n">
         <v>3.07</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>9.66</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45469.55208333334</v>
+        <v>45470.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>652.4</v>
+        <v>620.25</v>
       </c>
       <c r="I36" t="n">
         <v>623.2271208552983</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>11.59</v>
+        <v>6.09</v>
       </c>
       <c r="L36" t="n">
         <v>1.71</v>
       </c>
       <c r="M36" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="N36" t="n">
-        <v>1.08</v>
+        <v>3.74</v>
       </c>
       <c r="O36" t="n">
         <v>2.57</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>9.380000000000001</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45492.55208333334</v>
+        <v>45495.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>577.95</v>
+        <v>623.05</v>
       </c>
       <c r="I37" t="n">
         <v>605.7150394088828</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>6.82</v>
+        <v>-0.45</v>
       </c>
       <c r="L37" t="n">
         <v>5.15</v>
@@ -2550,7 +2993,7 @@
         <v>0.48</v>
       </c>
       <c r="N37" t="n">
-        <v>2.15</v>
+        <v>7.42</v>
       </c>
       <c r="O37" t="n">
         <v>-3.74</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>10.42</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>628</v>
+        <v>604.75</v>
       </c>
       <c r="I38" t="n">
         <v>607.8933907426126</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K38" t="n">
-        <v>0.79</v>
+        <v>-2.94</v>
       </c>
       <c r="L38" t="n">
         <v>8.02</v>
       </c>
       <c r="M38" t="n">
-        <v>0.84</v>
+        <v>2.68</v>
       </c>
       <c r="N38" t="n">
-        <v>1.54</v>
+        <v>3.03</v>
       </c>
       <c r="O38" t="n">
         <v>7.42</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>7.52</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45525.55208333334</v>
+        <v>45526.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>621.6</v>
+        <v>642.9</v>
       </c>
       <c r="I39" t="n">
         <v>637.9286524033117</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.79</v>
+        <v>-6.31</v>
       </c>
       <c r="L39" t="n">
-        <v>4.3</v>
+        <v>6.42</v>
       </c>
       <c r="M39" t="n">
         <v>1.35</v>
       </c>
       <c r="N39" t="n">
-        <v>3.74</v>
+        <v>3.97</v>
       </c>
       <c r="O39" t="n">
         <v>-3.03</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.17</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45565.55208333334</v>
+        <v>45566.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>686.5</v>
+        <v>679.8</v>
       </c>
       <c r="I40" t="n">
         <v>680.1620469216941</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K40" t="n">
-        <v>6.78</v>
+        <v>5.74</v>
       </c>
       <c r="L40" t="n">
         <v>3.44</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>5.78</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45574.55208333334</v>
+        <v>45575.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>694</v>
+        <v>705.1</v>
       </c>
       <c r="I41" t="n">
         <v>697.6383580239508</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.09</v>
+        <v>-3.72</v>
       </c>
       <c r="L41" t="n">
-        <v>4.12</v>
+        <v>5.24</v>
       </c>
       <c r="M41" t="n">
-        <v>0.51</v>
+        <v>0.75</v>
       </c>
       <c r="N41" t="n">
         <v>5.06</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>6.6</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>681</v>
+        <v>663.65</v>
       </c>
       <c r="I42" t="n">
         <v>670.8712591754127</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.42</v>
+        <v>-5.88</v>
       </c>
       <c r="L42" t="n">
-        <v>4.27</v>
+        <v>6.25</v>
       </c>
       <c r="M42" t="n">
         <v>0.21</v>
       </c>
       <c r="N42" t="n">
-        <v>2.68</v>
+        <v>3.6</v>
       </c>
       <c r="O42" t="n">
         <v>1.66</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45603.55208333334</v>
+        <v>45604.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>688.3</v>
+        <v>729.25</v>
       </c>
       <c r="I43" t="n">
         <v>698.9873937410879</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.71</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>4.78</v>
+        <v>9.98</v>
       </c>
       <c r="M43" t="n">
-        <v>0.77</v>
+        <v>3.15</v>
       </c>
       <c r="N43" t="n">
-        <v>3.37</v>
+        <v>6.2</v>
       </c>
       <c r="O43" t="n">
         <v>-3.6</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.18</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45663.38541666666</v>
+        <v>45663.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>851.15</v>
+        <v>845</v>
       </c>
       <c r="I44" t="n">
         <v>847.941778269411</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>59</v>
+        <v>59.16666666666666</v>
       </c>
       <c r="K44" t="n">
-        <v>16.72</v>
+        <v>15.87</v>
       </c>
       <c r="L44" t="n">
         <v>4.88</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.09</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45671.55208333334</v>
+        <v>45672.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>783.4</v>
+        <v>817.15</v>
       </c>
       <c r="I45" t="n">
         <v>813.4715027788162</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K45" t="n">
-        <v>7.29</v>
+        <v>3.3</v>
       </c>
       <c r="L45" t="n">
         <v>1.59</v>
@@ -3006,7 +3545,7 @@
         <v>0.47</v>
       </c>
       <c r="N45" t="n">
-        <v>3.34</v>
+        <v>3.78</v>
       </c>
       <c r="O45" t="n">
         <v>-2.89</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>8.84</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45678.38541666666</v>
+        <v>45678.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>769.9</v>
+        <v>760.5</v>
       </c>
       <c r="I46" t="n">
         <v>763.320639191723</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.78</v>
+        <v>-6.93</v>
       </c>
       <c r="L46" t="n">
-        <v>6.17</v>
+        <v>7.1</v>
       </c>
       <c r="M46" t="n">
         <v>0.01</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>8.52</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45691.38541666666</v>
+        <v>45691.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>808.25</v>
+        <v>813.15</v>
       </c>
       <c r="I47" t="n">
         <v>808.4217552171385</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.28</v>
+        <v>-6.92</v>
       </c>
       <c r="L47" t="n">
         <v>7.89</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>776.2</v>
+        <v>746.8</v>
       </c>
       <c r="I48" t="n">
         <v>773.7106088136584</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.54</v>
+        <v>-8.16</v>
       </c>
       <c r="L48" t="n">
-        <v>4.9</v>
+        <v>8.23</v>
       </c>
       <c r="M48" t="n">
         <v>0.05</v>
       </c>
       <c r="N48" t="n">
-        <v>2.99</v>
+        <v>3.74</v>
       </c>
       <c r="O48" t="n">
         <v>1.49</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>9.4</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45708.38541666666</v>
+        <v>45708.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>753.75</v>
+        <v>762.3</v>
       </c>
       <c r="I49" t="n">
         <v>758.0118151293163</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.93</v>
+        <v>-2.08</v>
       </c>
       <c r="L49" t="n">
         <v>3.91</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.88</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45743.38541666666</v>
+        <v>45743.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>800.5</v>
+        <v>790.7</v>
       </c>
       <c r="I50" t="n">
         <v>792.347301532287</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>34.83333333333334</v>
+        <v>35</v>
       </c>
       <c r="K50" t="n">
-        <v>5.01</v>
+        <v>3.73</v>
       </c>
       <c r="L50" t="n">
         <v>7.75</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>7.35</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>788.8</v>
+        <v>828.1</v>
       </c>
       <c r="I51" t="n">
         <v>816.5353797965458</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>15</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>0.24</v>
+        <v>-4.73</v>
       </c>
       <c r="L51" t="n">
         <v>5.97</v>
       </c>
       <c r="M51" t="n">
-        <v>3.23</v>
+        <v>4.34</v>
       </c>
       <c r="N51" t="n">
-        <v>2.88</v>
+        <v>6.11</v>
       </c>
       <c r="O51" t="n">
         <v>-2.14</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>9.66</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45772.38541666666</v>
+        <v>45772.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>792.45</v>
+        <v>784.85</v>
       </c>
       <c r="I52" t="n">
         <v>789.0295339635644</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.31</v>
+        <v>-5.22</v>
       </c>
       <c r="L52" t="n">
         <v>7.02</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>8.19</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45832.55208333334</v>
+        <v>45833.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>763.4</v>
+        <v>781.8</v>
       </c>
       <c r="I53" t="n">
         <v>767.5078102007495</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>60</v>
+        <v>60.83333333333334</v>
       </c>
       <c r="K53" t="n">
-        <v>2.73</v>
+        <v>0.39</v>
       </c>
       <c r="L53" t="n">
         <v>4.69</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>5.09</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45841.55208333334</v>
+        <v>45842.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>749</v>
+        <v>743.4</v>
       </c>
       <c r="I54" t="n">
         <v>747.9757720945993</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.2</v>
+        <v>-4.91</v>
       </c>
       <c r="L54" t="n">
-        <v>4.68</v>
+        <v>5.06</v>
       </c>
       <c r="M54" t="n">
         <v>0.49</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>4.6</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45854.55208333334</v>
+        <v>45855.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>750.65</v>
+        <v>755.75</v>
       </c>
       <c r="I55" t="n">
         <v>755.4334896380127</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.98</v>
+        <v>-1.66</v>
       </c>
       <c r="L55" t="n">
-        <v>1.41</v>
+        <v>2.35</v>
       </c>
       <c r="M55" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="N55" t="n">
         <v>2.48</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>3.62</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45862.55208333334</v>
+        <v>45863.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>753.6</v>
+        <v>743.15</v>
       </c>
       <c r="I56" t="n">
         <v>743.9277119075132</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.28</v>
+        <v>-1.67</v>
       </c>
       <c r="L56" t="n">
-        <v>1.25</v>
+        <v>2.17</v>
       </c>
       <c r="M56" t="n">
-        <v>0.02</v>
+        <v>0.4</v>
       </c>
       <c r="N56" t="n">
         <v>1.84</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>4.49</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45881.55208333334</v>
+        <v>45882.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>747.95</v>
+        <v>767.65</v>
       </c>
       <c r="I57" t="n">
         <v>765.9488718496884</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.65</v>
+        <v>-3.3</v>
       </c>
       <c r="L57" t="n">
-        <v>2.12</v>
+        <v>3.46</v>
       </c>
       <c r="M57" t="n">
         <v>0.8</v>
       </c>
       <c r="N57" t="n">
-        <v>1.51</v>
+        <v>2.98</v>
       </c>
       <c r="O57" t="n">
         <v>-0.88</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.2</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45895.38541666666</v>
+        <v>45895.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>779.05</v>
+        <v>769.9</v>
       </c>
       <c r="I58" t="n">
         <v>774.09348707509</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>1.49</v>
+        <v>0.29</v>
       </c>
       <c r="L58" t="n">
         <v>2.3</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>4.75</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45957.38541666666</v>
+        <v>45957.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>744.05</v>
+        <v>746.5</v>
       </c>
       <c r="I59" t="n">
         <v>745.1825132124985</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>61.83333333333334</v>
+        <v>62</v>
       </c>
       <c r="K59" t="n">
-        <v>3.36</v>
+        <v>3.04</v>
       </c>
       <c r="L59" t="n">
         <v>2.94</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>3.01</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45965.55208333334</v>
+        <v>45967.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>743</v>
+        <v>711.5</v>
       </c>
       <c r="I60" t="n">
         <v>727.4013117970245</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>8</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.47</v>
+        <v>-4.69</v>
       </c>
       <c r="L60" t="n">
-        <v>1.21</v>
+        <v>5.63</v>
       </c>
       <c r="M60" t="n">
-        <v>0.45</v>
+        <v>3.77</v>
       </c>
       <c r="N60" t="n">
-        <v>0.86</v>
+        <v>6.19</v>
       </c>
       <c r="O60" t="n">
         <v>1.56</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>5.79</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45980.55208333334</v>
+        <v>45981.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>719</v>
+        <v>736.4</v>
       </c>
       <c r="I61" t="n">
         <v>723.6723436595303</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.05</v>
+        <v>-3.5</v>
       </c>
       <c r="L61" t="n">
-        <v>3.77</v>
+        <v>4.15</v>
       </c>
       <c r="M61" t="n">
         <v>0.65</v>
       </c>
       <c r="N61" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="O61" t="n">
         <v>-6.19</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>5.04</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45999.38541666666</v>
+        <v>45999.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>723.6</v>
+        <v>717.2</v>
       </c>
       <c r="I62" t="n">
         <v>721.946066179338</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.74</v>
+        <v>-2.61</v>
       </c>
       <c r="L62" t="n">
-        <v>2.68</v>
+        <v>3.01</v>
       </c>
       <c r="M62" t="n">
         <v>0.68</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>4.07</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>730.6</v>
+        <v>739.7</v>
       </c>
       <c r="I63" t="n">
         <v>739.321422912428</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.87</v>
+        <v>-3.14</v>
       </c>
       <c r="L63" t="n">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="M63" t="n">
-        <v>0.37</v>
+        <v>0.6</v>
       </c>
       <c r="N63" t="n">
         <v>1.5</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,25 +4835,25 @@
         <v>4.45</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46028.55208333334</v>
+        <v>46029.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>725.35</v>
+        <v>711.4</v>
       </c>
       <c r="I64" t="n">
         <v>722.8116896092587</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.94</v>
+        <v>-3.83</v>
       </c>
       <c r="L64" t="n">
-        <v>2.62</v>
+        <v>4.92</v>
       </c>
       <c r="M64" t="n">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="N64" t="n">
         <v>2.51</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>4.65</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>666.95</v>
+        <v>682.95</v>
       </c>
       <c r="I65" t="n">
         <v>675.384834691016</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K65" t="n">
-        <v>6.25</v>
+        <v>4</v>
       </c>
       <c r="L65" t="n">
         <v>1.36</v>
       </c>
       <c r="M65" t="n">
-        <v>1.37</v>
+        <v>1.96</v>
       </c>
       <c r="N65" t="n">
-        <v>1.82</v>
+        <v>2.26</v>
       </c>
       <c r="O65" t="n">
         <v>-1.56</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>7.04</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46072.38541666666</v>
+        <v>46072.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>679.75</v>
+        <v>669.8</v>
       </c>
       <c r="I66" t="n">
         <v>673.6445755058446</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.47</v>
+        <v>-1.93</v>
       </c>
       <c r="L66" t="n">
-        <v>1.74</v>
+        <v>2.17</v>
       </c>
       <c r="M66" t="n">
         <v>0.7</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>5.95</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>600.7</v>
+        <v>641.75</v>
       </c>
       <c r="I67" t="n">
         <v>617.6780756213333</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>47</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K67" t="n">
-        <v>10.32</v>
+        <v>4.19</v>
       </c>
       <c r="L67" t="n">
         <v>2.27</v>
@@ -4260,7 +5063,7 @@
         <v>4.55</v>
       </c>
       <c r="N67" t="n">
-        <v>3.6</v>
+        <v>6.37</v>
       </c>
       <c r="O67" t="n">
         <v>-3.33</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>9.42</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>664.8</v>
+        <v>638.5</v>
       </c>
       <c r="I68" t="n">
         <v>642.0100626486176</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K68" t="n">
-        <v>3.59</v>
+        <v>-0.51</v>
       </c>
       <c r="L68" t="n">
         <v>3.7</v>
@@ -4317,7 +5132,7 @@
         <v>3.72</v>
       </c>
       <c r="N68" t="n">
-        <v>3.15</v>
+        <v>4.48</v>
       </c>
       <c r="O68" t="n">
         <v>6.37</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46182.55208333334</v>
+        <v>46183.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>666.05</v>
+        <v>676.75</v>
       </c>
       <c r="I69" t="n">
         <v>674.1733181066178</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K69" t="n">
-        <v>-4.31</v>
+        <v>-5.99</v>
       </c>
       <c r="L69" t="n">
-        <v>5.7</v>
+        <v>6.46</v>
       </c>
       <c r="M69" t="n">
         <v>1.41</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>5.91</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46245.55208333334</v>
+        <v>46246.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>724.95</v>
+        <v>713.65</v>
       </c>
       <c r="I70" t="n">
         <v>722.2233606093356</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>62.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K70" t="n">
-        <v>7.12</v>
+        <v>5.45</v>
       </c>
       <c r="L70" t="n">
         <v>3.35</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>4.21</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46268.38541666666</v>
+        <v>46268.55208333334</v>
       </c>
       <c r="H71" t="n">
-        <v>726.45</v>
+        <v>731</v>
       </c>
       <c r="I71" t="n">
         <v>728.495128516225</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K71" t="n">
-        <v>-1.79</v>
+        <v>-2.43</v>
       </c>
       <c r="L71" t="n">
         <v>3.29</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>3.9</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46290.55208333334</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="I72" t="n">
         <v>715.8121000872467</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>22</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.68</v>
+        <v>-2.19</v>
       </c>
       <c r="L72" t="n">
         <v>3.32</v>
@@ -4545,7 +5408,7 @@
         <v>1.08</v>
       </c>
       <c r="N72" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="O72" t="n">
         <v>0.65</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>4.4</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46309.55208333334</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>729</v>
+        <v>746.1</v>
       </c>
       <c r="I73" t="n">
         <v>739.5333079191163</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K73" t="n">
-        <v>-1.96</v>
+        <v>-4.35</v>
       </c>
       <c r="L73" t="n">
-        <v>3.92</v>
+        <v>5.25</v>
       </c>
       <c r="M73" t="n">
         <v>0.64</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4662,6 +5549,12 @@
       <c r="Q74" t="n">
         <v>16</v>
       </c>
+      <c r="R74" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6764,7 +7657,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.2</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="6">
@@ -6774,7 +7667,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -6784,7 +7677,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110.2</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8">
@@ -6794,7 +7687,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -6804,7 +7697,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.9</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="10">
@@ -6814,7 +7707,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="11">
@@ -6854,7 +7747,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.39</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="15">
@@ -6864,7 +7757,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.34</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="16">
@@ -6874,7 +7767,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.57</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="17">
@@ -6884,7 +7777,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>45.34</v>
+        <v>38.48</v>
       </c>
     </row>
     <row r="18">
@@ -6894,7 +7787,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>40.3</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="19">
@@ -6904,7 +7797,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.22</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="20">
@@ -6914,7 +7807,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.16</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="21">
@@ -6924,7 +7817,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.92</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="22">
@@ -6934,7 +7827,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -6944,7 +7837,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -6954,7 +7847,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="25">
@@ -6964,7 +7857,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.64</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="26">
@@ -6974,7 +7867,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.05</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="27">
@@ -6984,7 +7877,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.73</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="28">
@@ -6994,7 +7887,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
